--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104492_W4.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104492_W4.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T. HLINASON</t>
+          <t>J. JAWORSKI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7885</v>
+        <v>4.4467</v>
       </c>
       <c r="E2" t="n">
-        <v>1.1164</v>
+        <v>2.8857</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6721</v>
+        <v>1.561</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2023</v>
+        <v>3.1227</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.0981</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8957000000000001</v>
+        <v>3.1139</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.4062</v>
+        <v>1.8141</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.5928</v>
+        <v>-0.6797</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1866</v>
+        <v>2.4938</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2038</v>
+        <v>1.3087</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5053</v>
+        <v>0.6886</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7091</v>
+        <v>0.6201</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2591</v>
+        <v>0.2753</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5375</v>
+        <v>0.5269</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7216</v>
+        <v>-0.2516</v>
       </c>
       <c r="V2" t="n">
-        <v>1.639</v>
+        <v>-0.5447</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2534</v>
+        <v>0.5447</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3856</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2604</v>
+        <v>3.1369</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9297</v>
+        <v>1.7596</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3307</v>
+        <v>1.3773</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2313</v>
+        <v>1.2358</v>
       </c>
       <c r="H3" t="n">
-        <v>1.29</v>
+        <v>1.2923</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6122</v>
+        <v>1.6066</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8658</v>
+        <v>0.8618</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7463</v>
+        <v>0.7447</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3808</v>
+        <v>-0.3708</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4241</v>
+        <v>0.4305</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.805</v>
+        <v>-0.8012</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4413</v>
+        <v>0.3077</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3176</v>
+        <v>0.1531</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1237</v>
+        <v>0.1546</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. JAWORSKI</t>
+          <t>S. LAZAREVIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7933</v>
+        <v>2.2246</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7308</v>
+        <v>2.1002</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0624</v>
+        <v>0.1244</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1475</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0131</v>
+        <v>0.485</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1345</v>
+        <v>-0.5599</v>
       </c>
       <c r="J4" t="n">
-        <v>1.862</v>
+        <v>0.8114</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.662</v>
+        <v>0.9308</v>
       </c>
       <c r="L4" t="n">
-        <v>2.524</v>
+        <v>-0.1194</v>
       </c>
       <c r="M4" t="n">
-        <v>1.2856</v>
+        <v>-0.8863</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6751</v>
+        <v>-0.4458</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6105</v>
+        <v>-0.4405</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3958</v>
+        <v>0.9337</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6775</v>
+        <v>1.2888</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7183</v>
+        <v>-0.3551</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. LAZAREVIC</t>
+          <t>T. HLINASON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6472</v>
+        <v>1.9694</v>
       </c>
       <c r="E5" t="n">
-        <v>2.4839</v>
+        <v>-0.2346</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1632</v>
+        <v>2.204</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0876</v>
+        <v>-0.1922</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4775</v>
+        <v>-1.0999</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0.9077</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8204</v>
+        <v>-0.4246</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9351</v>
+        <v>-0.6108</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1147</v>
+        <v>0.1862</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.908</v>
+        <v>0.2324</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4576</v>
+        <v>-0.4891</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4504</v>
+        <v>0.7215</v>
       </c>
       <c r="P5" t="n">
-        <v>1.361</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3737</v>
+        <v>1.4379</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6635</v>
+        <v>1.2191</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2898</v>
+        <v>0.2189</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.6342</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9033</v>
+        <v>1.7828</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4069</v>
+        <v>2.6901</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5036</v>
+        <v>-0.9073</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5011</v>
+        <v>0.502</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1573</v>
+        <v>-0.1579</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6584</v>
+        <v>0.66</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6787</v>
+        <v>0.658</v>
       </c>
       <c r="K6" t="n">
-        <v>0.159</v>
+        <v>0.1444</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1776</v>
+        <v>-0.156</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P6" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5195</v>
+        <v>1.3914</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4748</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0446</v>
+        <v>0.6066</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.4783</v>
+        <v>-1.4764</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.8245</v>
+        <v>1.4833</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2806</v>
+        <v>-0.6485</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1051</v>
+        <v>2.1318</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1437</v>
+        <v>-1.1511</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.3273</v>
+        <v>-2.34</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1835</v>
+        <v>1.189</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.5284</v>
+        <v>-1.5543</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.2001</v>
+        <v>-2.2245</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3847</v>
+        <v>0.4032</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1272</v>
+        <v>-0.1155</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>1.6241</v>
+        <v>1.2961</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3308</v>
+        <v>1.0031</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2934</v>
+        <v>0.2929</v>
       </c>
       <c r="V7" t="n">
-        <v>2.0246</v>
+        <v>2.0212</v>
       </c>
       <c r="W7" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="8">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4153</v>
+        <v>0.8809</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7301</v>
+        <v>-1.354</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1454</v>
+        <v>2.2349</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8153</v>
+        <v>2.8057</v>
       </c>
       <c r="H8" t="n">
-        <v>3.0446</v>
+        <v>3.0444</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2293</v>
+        <v>-0.2388</v>
       </c>
       <c r="J8" t="n">
-        <v>2.3479</v>
+        <v>2.3155</v>
       </c>
       <c r="K8" t="n">
-        <v>3.0304</v>
+        <v>3.0164</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6825</v>
+        <v>-0.7009</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4674</v>
+        <v>0.4901</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0142</v>
+        <v>0.028</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3605</v>
+        <v>0.1255</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4506</v>
+        <v>-0.0258</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0901</v>
+        <v>0.1513</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3427</v>
+        <v>0.4118</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2383</v>
+        <v>1.1251</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8956</v>
+        <v>-0.7133</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6455</v>
+        <v>-1.6474</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5499000000000001</v>
+        <v>-0.5432</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0956</v>
+        <v>-1.1042</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2415</v>
+        <v>-0.2568</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3637</v>
+        <v>0.362</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6052</v>
+        <v>-0.6188</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4039</v>
+        <v>-1.3906</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9135</v>
+        <v>-0.9052</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.6235000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3871</v>
+        <v>0.2925</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1739</v>
+        <v>0.3311</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. FONT</t>
+          <t>H. FREY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0387</v>
+        <v>0.3699</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0149</v>
+        <v>-0.0694</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0537</v>
+        <v>0.4393</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1185</v>
+        <v>2.4452</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1559</v>
+        <v>1.6426</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0373</v>
+        <v>0.8026</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0546</v>
+        <v>3.1736</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0173</v>
+        <v>1.9305</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0373</v>
+        <v>1.243</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1732</v>
+        <v>-0.7284</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1732</v>
+        <v>-0.2879</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0.4405</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2268</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-4.5526</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2268</v>
+        <v>1.5934</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0696</v>
+        <v>-0.2056</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0696</v>
+        <v>0.0624</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0.268</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H. FREY</t>
+          <t>A. FONT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.733</v>
+        <v>0.1585</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9874000000000001</v>
+        <v>0.1032</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2545</v>
+        <v>0.0553</v>
       </c>
       <c r="G11" t="n">
-        <v>2.4494</v>
+        <v>-0.1179</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6391</v>
+        <v>-0.1551</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8103</v>
+        <v>0.0372</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2001</v>
+        <v>0.0545</v>
       </c>
       <c r="K11" t="n">
-        <v>1.9395</v>
+        <v>0.0172</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2607</v>
+        <v>0.0372</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7507</v>
+        <v>-0.1724</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3003</v>
+        <v>-0.1724</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4504</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.9488</v>
+        <v>0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.5367</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5878</v>
+        <v>0.2276</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3262</v>
+        <v>0.0487</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9043</v>
+        <v>0.0487</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4219</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.9747</v>
+        <v>-3.1543</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0105</v>
+        <v>-2.3478</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9641999999999999</v>
+        <v>-0.8065</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.1359</v>
+        <v>-2.1321</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1831</v>
+        <v>0.1919</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.319</v>
+        <v>-2.324</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.7584</v>
+        <v>-1.7761</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6407</v>
+        <v>0.6378</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.3991</v>
+        <v>-2.4138</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3776</v>
+        <v>-0.356</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O12" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5607</v>
+        <v>0.2462</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1179</v>
+        <v>0.5664</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4428</v>
+        <v>-0.3202</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>12.3062</v>
+        <v>13.7105</v>
       </c>
       <c r="E13" t="n">
-        <v>4.8825</v>
+        <v>6.009599999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>7.423699999999998</v>
+        <v>7.700900000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>4.8111</v>
+        <v>4.7958</v>
       </c>
       <c r="H13" t="n">
-        <v>2.358899999999999</v>
+        <v>2.3689</v>
       </c>
       <c r="I13" t="n">
-        <v>2.4522</v>
+        <v>2.427</v>
       </c>
       <c r="J13" t="n">
-        <v>6.641400000000001</v>
+        <v>6.421900000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>4.4966</v>
+        <v>4.3859</v>
       </c>
       <c r="L13" t="n">
-        <v>2.1448</v>
+        <v>2.0359</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.8303</v>
+        <v>-1.6261</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.1375</v>
+        <v>-2.0169</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3071</v>
+        <v>0.391</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2682</v>
+        <v>2.2762</v>
       </c>
       <c r="Q13" t="n">
-        <v>-13.61</v>
+        <v>-13.6579</v>
       </c>
       <c r="R13" t="n">
-        <v>15.8781</v>
+        <v>15.9341</v>
       </c>
       <c r="S13" t="n">
-        <v>5.0659</v>
+        <v>6.480399999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>4.4914</v>
+        <v>5.920000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5745</v>
+        <v>0.5604999999999998</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1608000000000001</v>
+        <v>0.1579000000000002</v>
       </c>
       <c r="W13" t="n">
-        <v>7.359599999999999</v>
+        <v>7.3255</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.1989</v>
+        <v>-7.167899999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.2894</v>
+        <v>3.2367</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4347</v>
+        <v>2.4159</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8547</v>
+        <v>0.8208</v>
       </c>
       <c r="G14" t="n">
-        <v>1.826</v>
+        <v>1.8345</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9277</v>
+        <v>0.9331</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8983</v>
+        <v>0.9014</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3904</v>
+        <v>1.3732</v>
       </c>
       <c r="K14" t="n">
-        <v>1.7317</v>
+        <v>1.7237</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.3413</v>
+        <v>-0.3505</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4356</v>
+        <v>0.4613</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="O14" t="n">
-        <v>1.2396</v>
+        <v>1.2518</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.0564</v>
+        <v>-1.1229</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0484</v>
+        <v>-0.0468</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0081</v>
+        <v>-1.0761</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1058</v>
+        <v>2.48</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7249</v>
+        <v>2.8159</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6191</v>
+        <v>-0.3359</v>
       </c>
       <c r="G15" t="n">
-        <v>3.805</v>
+        <v>3.815</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3953</v>
+        <v>1.3985</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4097</v>
+        <v>2.4165</v>
       </c>
       <c r="J15" t="n">
-        <v>2.429</v>
+        <v>2.4209</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1602</v>
+        <v>1.1549</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2688</v>
+        <v>1.2661</v>
       </c>
       <c r="M15" t="n">
-        <v>1.376</v>
+        <v>1.3941</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2351</v>
+        <v>0.2437</v>
       </c>
       <c r="O15" t="n">
-        <v>1.1409</v>
+        <v>1.1504</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1094</v>
+        <v>-0.7431</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4869</v>
+        <v>-0.3695</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6224</v>
+        <v>-0.3736</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W15" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.5068</v>
+        <v>-2.4945</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6339</v>
+        <v>1.78</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7758</v>
+        <v>-0.1001</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4097</v>
+        <v>1.8801</v>
       </c>
       <c r="G16" t="n">
-        <v>3.2774</v>
+        <v>3.2791</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3347</v>
+        <v>0.3387</v>
       </c>
       <c r="I16" t="n">
-        <v>2.9427</v>
+        <v>2.9404</v>
       </c>
       <c r="J16" t="n">
-        <v>2.4845</v>
+        <v>2.4599</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9973</v>
+        <v>0.9858</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4873</v>
+        <v>1.4741</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7929</v>
+        <v>0.8192</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6626</v>
+        <v>-0.6471</v>
       </c>
       <c r="O16" t="n">
-        <v>1.4555</v>
+        <v>1.4663</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.0291</v>
+        <v>-0.886</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7652</v>
+        <v>-0.0561</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.2639</v>
+        <v>-0.83</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1765</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5703</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7468</v>
+        <v>-0.6227</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4278</v>
+        <v>1.4203</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2436</v>
+        <v>-0.2604</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6714</v>
+        <v>1.6807</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1335</v>
+        <v>1.1025</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3872</v>
+        <v>0.3577</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7463</v>
+        <v>0.7447</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2943</v>
+        <v>0.3178</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6308</v>
+        <v>-0.6182</v>
       </c>
       <c r="O17" t="n">
-        <v>0.925</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4455</v>
+        <v>-0.3518</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0907</v>
+        <v>0.0926</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5363</v>
+        <v>-0.4444</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W17" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. OKOYE</t>
+          <t>C. ORTEGA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5063</v>
+        <v>-0.6913</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7339</v>
+        <v>0.3393</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2276</v>
+        <v>-1.0306</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.4957</v>
+        <v>-0.2094</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.4428</v>
+        <v>-1.3072</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0529</v>
+        <v>1.0978</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.8409</v>
+        <v>0.4509</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.9447</v>
+        <v>0.0862</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1038</v>
+        <v>0.3647</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6548</v>
+        <v>-0.6603</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5019</v>
+        <v>-1.3934</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1567</v>
+        <v>0.7331</v>
       </c>
       <c r="P18" t="n">
-        <v>2.0415</v>
+        <v>0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2683</v>
+        <v>0.4553</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9479</v>
+        <v>-0.9372</v>
       </c>
       <c r="T18" t="n">
-        <v>1.3338</v>
+        <v>-0.1116</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3859</v>
+        <v>-0.8256</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,22 +1891,22 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8754999999999999</v>
+        <v>-0.8085</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2087</v>
+        <v>-0.2091</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6667999999999999</v>
+        <v>-0.5994</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9354</v>
+        <v>-0.9315</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3463</v>
+        <v>-0.3447</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1918,31 +1918,31 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9354</v>
+        <v>-0.9315</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3463</v>
+        <v>-0.3447</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1669</v>
+        <v>-0.1046</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2087</v>
+        <v>-0.2091</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0417</v>
+        <v>0.1046</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. ORTEGA</t>
+          <t>S. OKOYE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9638</v>
+        <v>-1.0623</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1092</v>
+        <v>-2.8287</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.073</v>
+        <v>1.7665</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2165</v>
+        <v>-3.5011</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3147</v>
+        <v>-2.4495</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0982</v>
+        <v>-1.0516</v>
       </c>
       <c r="J20" t="n">
-        <v>0.457</v>
+        <v>-2.877</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0866</v>
+        <v>-2.9657</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3705</v>
+        <v>0.0887</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6735</v>
+        <v>-0.6241</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4012</v>
+        <v>0.5162</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7277</v>
+        <v>-1.1403</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4537</v>
+        <v>2.0487</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4537</v>
+        <v>2.2763</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.201</v>
+        <v>0.3902</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3478</v>
+        <v>0.2759</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8532</v>
+        <v>0.1143</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9233</v>
+        <v>-2.2464</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9314</v>
+        <v>0.5553</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.8547</v>
+        <v>-2.8017</v>
       </c>
       <c r="G21" t="n">
-        <v>1.2479</v>
+        <v>1.2487</v>
       </c>
       <c r="H21" t="n">
-        <v>2.2901</v>
+        <v>2.2837</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0422</v>
+        <v>-1.035</v>
       </c>
       <c r="J21" t="n">
-        <v>2.7214</v>
+        <v>2.7089</v>
       </c>
       <c r="K21" t="n">
-        <v>2.6841</v>
+        <v>2.6717</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4735</v>
+        <v>-1.4603</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.394</v>
+        <v>-0.3881</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4413</v>
+        <v>0.1195</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3176</v>
+        <v>-0.0351</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1237</v>
+        <v>0.1546</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.0246</v>
+        <v>-2.0212</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="22">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0137</v>
+        <v>-2.6436</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9349</v>
+        <v>-2.2978</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0788</v>
+        <v>-0.3458</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.7101</v>
+        <v>-3.7086</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3089</v>
+        <v>-0.3047</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.4012</v>
+        <v>-3.4039</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.2525</v>
+        <v>-2.2627</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0693</v>
+        <v>0.0689</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.3218</v>
+        <v>-2.3317</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4576</v>
+        <v>-1.4458</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3781</v>
+        <v>-0.3736</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>1.0159</v>
+        <v>0.382</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3176</v>
+        <v>-0.0351</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6983</v>
+        <v>0.4171</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.684</v>
+        <v>-4.4262</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.931</v>
+        <v>-5.0835</v>
       </c>
       <c r="F23" t="n">
-        <v>0.247</v>
+        <v>0.6574</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.6907</v>
+        <v>-4.6821</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.6681</v>
+        <v>-1.6659</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.0227</v>
+        <v>-3.0162</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.0496</v>
+        <v>-3.0683</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.1859</v>
+        <v>-2.1966</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.8637</v>
+        <v>-0.8718</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.6411</v>
+        <v>-1.6138</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5178</v>
+        <v>0.5306</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.159</v>
+        <v>-2.1444</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2032</v>
+        <v>0.0558</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1089</v>
+        <v>-0.0073</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3121</v>
+        <v>0.0631</v>
       </c>
       <c r="V23" t="n">
-        <v>2.0246</v>
+        <v>2.0212</v>
       </c>
       <c r="W23" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X23" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.1922</v>
+        <v>-6.2647</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.6098</v>
+        <v>-3.8397</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.5823</v>
+        <v>-2.425</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.3469</v>
+        <v>-3.3607</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.9825</v>
+        <v>-0.9903999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.3644</v>
+        <v>-2.3702</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6425999999999999</v>
+        <v>-0.6822</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1519</v>
+        <v>0.1304</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7945</v>
+        <v>-0.8126</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.7043</v>
+        <v>-2.6784</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1344</v>
+        <v>-1.1209</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.5699</v>
+        <v>-1.5576</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2594</v>
+        <v>-0.309</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8861</v>
+        <v>-0.0585</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3732</v>
+        <v>-0.2505</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W24" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-12.3062</v>
+        <v>-10.7372</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.4236</v>
+        <v>-7.7007</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.8825</v>
+        <v>-3.036299999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.811199999999999</v>
+        <v>-4.7958</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.3591</v>
+        <v>-2.3688</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.452199999999999</v>
+        <v>-2.4269</v>
       </c>
       <c r="J25" t="n">
-        <v>1.830200000000001</v>
+        <v>1.6261</v>
       </c>
       <c r="K25" t="n">
-        <v>2.137699999999999</v>
+        <v>2.017</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.3072999999999998</v>
+        <v>-0.3911000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-6.6414</v>
+        <v>-6.421799999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>-4.4965</v>
+        <v>-4.3861</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.145</v>
+        <v>-2.035900000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.2684</v>
+        <v>-2.2764</v>
       </c>
       <c r="Q25" t="n">
-        <v>-15.8783</v>
+        <v>-15.9341</v>
       </c>
       <c r="R25" t="n">
-        <v>13.61</v>
+        <v>13.658</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.065799999999999</v>
+        <v>-3.5071</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5744999999999998</v>
+        <v>-0.5606</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.491399999999999</v>
+        <v>-2.9465</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.1607</v>
+        <v>-0.1577999999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>7.1989</v>
+        <v>7.167899999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>-7.359599999999999</v>
+        <v>-7.3257</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104492_W4.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104492_W4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104492_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104492_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104492_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104492_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104492_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104492_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104492_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104492_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104492_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104492_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104492_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-7.167899999999999</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104492_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-2.4945</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104492_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104492_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104492_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104492_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104492_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104492_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104492_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104492_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104492_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104492_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-7.3257</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
